--- a/public/downloads/handball-statistik-vorlage.xlsx
+++ b/public/downloads/handball-statistik-vorlage.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Start" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Kader" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Spielprotokoll" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Auswertung" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Saison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kader" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spielprotokoll" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auswertung" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wurfbild" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saison" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Spiele">Saison!$A$4:$A$33</definedName>
@@ -26,9 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0;-0;&quot;–&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;;&quot;–&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -141,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -163,11 +165,64 @@
         <color rgb="00C9C2B6"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C2B6"/>
+      </left>
+      <top style="thin">
+        <color rgb="00C9C2B6"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9C2B6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C2B6"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C2B6"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9C2B6"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C2B6"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00C9C2B6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9C2B6"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9C2B6"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9C2B6"/>
+      </top>
+    </border>
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="00C9C2B6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,6 +330,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -658,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D27"/>
+  <dimension ref="B1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -776,7 +862,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Blatt „Auswertung“ oben das Spiel auswählen: Quoten, Torwartwerte und das Ergebnis stehen da. Das Blatt „Saison“ zeigt dieselben Werte über alle Spiele.</t>
+          <t>Blatt „Auswertung“ oben das Spiel auswählen: Quoten, Torwartwerte und das Ergebnis stehen da. „Wurfbild“ zeigt, aus welcher Zone getroffen wird, „Saison“ alle Werte über alle Spiele.</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -914,22 +1000,39 @@
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="16" t="inlineStr">
         <is>
+          <t>Wurfbild</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Wo getroffen wird – je Wurfzone</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Rechnet automatisch – Spiel und Spieler wählbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
           <t>Saison</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Spieleliste und Saisonwerte</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Spiele einträgst du, der Rest rechnet</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Platz: 20 Kaderplätze, 400 Aktionszeilen, 30 Spiele. Reicht das nicht, markierst du die letzte Zeile und ziehst sie nach unten – die Formeln wandern mit. Eigene Vereinsfarben: Zellen markieren und wie gewohnt einfärben, an den Formeln ändert das nichts.</t>
         </is>
@@ -937,12 +1040,12 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
@@ -1690,28 +1793,60 @@
       <c r="G17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Sp1</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>11</v>
+      </c>
       <c r="D18" s="29">
         <f>IF($C18="","",IFERROR(INDEX(Kader!$B$4:$B$23,MATCH($C18,Kader!$A$4:$A$23,0)),"Nr. nicht im Kader"))</f>
         <v/>
       </c>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Tor</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Tempogegenstoß</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n"/>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Sp1</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>7</v>
+      </c>
       <c r="D19" s="29">
         <f>IF($C19="","",IFERROR(INDEX(Kader!$B$4:$B$23,MATCH($C19,Kader!$A$4:$A$23,0)),"Nr. nicht im Kader"))</f>
         <v/>
       </c>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>Fehlwurf</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="26" t="n"/>
@@ -7916,6 +8051,1924 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00F97316"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="18">
+        <f>IF(Start!$C$5="","Wurfbild",Start!$C$5&amp;"  ·  Wurfbild")</f>
+        <v/>
+      </c>
+      <c r="N1" s="19">
+        <f>IF(Start!$C$6="","","Saison "&amp;Start!$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Wo deine Mannschaft trifft – und wo nicht. Zählt jeden Wurf aus dem Spielprotokoll, der eine Zone trägt (Feldwürfe und Siebenmeter). Spiel leer lassen = ganze Saison, Nr. leer lassen = ganze Mannschaft. Hier trägst du außer diesen beiden Feldern nichts ein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Spiel:</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n"/>
+      <c r="C3" s="28">
+        <f>IF($B$3="","ganze Saison","")</f>
+        <v/>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
+        <is>
+          <t>Nr.:</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="43">
+        <f>IF($F$3="","ganze Mannschaft",IFERROR(INDEX(Kader!$B$4:$B$23,MATCH($F$3,Kader!$A$4:$A$23,0)),"Nr. nicht im Kader"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="J5" s="44" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="K5" s="44" t="inlineStr">
+        <is>
+          <t>Würfe</t>
+        </is>
+      </c>
+      <c r="L5" s="44" t="inlineStr">
+        <is>
+          <t>Tore</t>
+        </is>
+      </c>
+      <c r="M5" s="44" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="N5" s="44" t="inlineStr">
+        <is>
+          <t>Anteil</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>T O R</t>
+        </is>
+      </c>
+      <c r="J6" s="46" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="K6" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L6" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J6,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M6" s="47">
+        <f>IFERROR($L6/$K6,"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="38">
+        <f>IFERROR($K6/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="B7" s="48">
+        <f>J6</f>
+        <v/>
+      </c>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="48">
+        <f>J7</f>
+        <v/>
+      </c>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="48">
+        <f>J11</f>
+        <v/>
+      </c>
+      <c r="G7" s="49" t="n"/>
+      <c r="J7" s="46" t="inlineStr">
+        <is>
+          <t>Kreis</t>
+        </is>
+      </c>
+      <c r="K7" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L7" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J7,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M7" s="47">
+        <f>IFERROR($L7/$K7,"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="38">
+        <f>IFERROR($K7/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="B8" s="50">
+        <f>IF($K6=0,"keine Würfe","Tore / Würfe: "&amp;$L6&amp;" / "&amp;$K6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="51" t="n"/>
+      <c r="D8" s="50">
+        <f>IF($K7=0,"keine Würfe","Tore / Würfe: "&amp;$L7&amp;" / "&amp;$K7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="51" t="n"/>
+      <c r="F8" s="50">
+        <f>IF($K11=0,"keine Würfe","Tore / Würfe: "&amp;$L11&amp;" / "&amp;$K11)</f>
+        <v/>
+      </c>
+      <c r="G8" s="51" t="n"/>
+      <c r="J8" s="46" t="inlineStr">
+        <is>
+          <t>Rückraum</t>
+        </is>
+      </c>
+      <c r="K8" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L8" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J8,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M8" s="47">
+        <f>IFERROR($L8/$K8,"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="38">
+        <f>IFERROR($K8/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="52">
+        <f>IF($K6=0,"",$M6)</f>
+        <v/>
+      </c>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="52">
+        <f>IF($K7=0,"",$M7)</f>
+        <v/>
+      </c>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="52">
+        <f>IF($K11=0,"",$M11)</f>
+        <v/>
+      </c>
+      <c r="G9" s="53" t="n"/>
+      <c r="J9" s="46" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
+      </c>
+      <c r="K9" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L9" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J9,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M9" s="47">
+        <f>IFERROR($L9/$K9,"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="38">
+        <f>IFERROR($K9/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="B10" s="48">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="J10" s="46" t="inlineStr">
+        <is>
+          <t>Tempogegenstoß</t>
+        </is>
+      </c>
+      <c r="K10" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L10" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J10,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M10" s="47">
+        <f>IFERROR($L10/$K10,"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="38">
+        <f>IFERROR($K10/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="B11" s="50">
+        <f>IF($K9=0,"keine Würfe","Tore / Würfe: "&amp;$L9&amp;" / "&amp;$K9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="51" t="n"/>
+      <c r="J11" s="46" t="inlineStr">
+        <is>
+          <t>Siebenmeter</t>
+        </is>
+      </c>
+      <c r="K11" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L11" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,$J11,Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M11" s="47">
+        <f>IFERROR($L11/$K11,"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="38">
+        <f>IFERROR($K11/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="52">
+        <f>IF($K9=0,"",$M9)</f>
+        <v/>
+      </c>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="J12" s="46" t="inlineStr">
+        <is>
+          <t>ohne Zone</t>
+        </is>
+      </c>
+      <c r="K12" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")</f>
+        <v/>
+      </c>
+      <c r="L12" s="37">
+        <f>COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($F$3="","&lt;&gt;",$F$3),Spielprotokoll!$F$4:$F$403,"",Spielprotokoll!$E$4:$E$403,"7m Tor")</f>
+        <v/>
+      </c>
+      <c r="M12" s="47">
+        <f>IFERROR($L12/$K12,"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="38">
+        <f>IFERROR($K12/$K$13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="B13" s="48">
+        <f>J8</f>
+        <v/>
+      </c>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n"/>
+      <c r="F13" s="54" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="J13" s="40" t="inlineStr">
+        <is>
+          <t>Gesamt</t>
+        </is>
+      </c>
+      <c r="K13" s="41">
+        <f>SUM(K6:K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="41">
+        <f>SUM(L6:L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="57">
+        <f>IFERROR($L13/$K13,"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="42">
+        <f>IF($K13=0,"",1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="B14" s="50">
+        <f>IF($K8=0,"keine Würfe","Tore / Würfe: "&amp;$L8&amp;" / "&amp;$K8)</f>
+        <v/>
+      </c>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>„ohne Zone“ = Würfe, bei denen im Protokoll keine Zone steht. Je weniger davon, desto aussagekräftiger das Bild links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="52">
+        <f>IF($K8=0,"",$M8)</f>
+        <v/>
+      </c>
+      <c r="C15" s="56" t="n"/>
+      <c r="D15" s="56" t="n"/>
+      <c r="E15" s="56" t="n"/>
+      <c r="F15" s="56" t="n"/>
+      <c r="G15" s="53" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="B16" s="48">
+        <f>J10</f>
+        <v/>
+      </c>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n"/>
+      <c r="G16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="B17" s="50">
+        <f>IF($K10=0,"keine Würfe","Tore / Würfe: "&amp;$L10&amp;" / "&amp;$K10)</f>
+        <v/>
+      </c>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="51" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="52">
+        <f>IF($K10=0,"",$M10)</f>
+        <v/>
+      </c>
+      <c r="C18" s="56" t="n"/>
+      <c r="D18" s="56" t="n"/>
+      <c r="E18" s="56" t="n"/>
+      <c r="F18" s="56" t="n"/>
+      <c r="G18" s="53" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Wurfbild je Spieler</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Tore/Würfe und Quote je Zone – für das oben gewählte Spiel (leer = ganze Saison). Die Nr. oben gilt hier nicht: die Liste zeigt immer den ganzen Kader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>Spieler</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Außen</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>Kreis</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="34" t="inlineStr">
+        <is>
+          <t>Rückraum</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="34" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
+      </c>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="34" t="inlineStr">
+        <is>
+          <t>Tempogegenstoß</t>
+        </is>
+      </c>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="34" t="inlineStr">
+        <is>
+          <t>Siebenmeter</t>
+        </is>
+      </c>
+      <c r="N23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>T / W</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="36">
+        <f>IF(Kader!$A4="","",Kader!$A4)</f>
+        <v/>
+      </c>
+      <c r="B25" s="29">
+        <f>IF(Kader!$B4="","",Kader!$B4)</f>
+        <v/>
+      </c>
+      <c r="C25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M25" s="36">
+        <f>IF($A25="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="47">
+        <f>IF($A25="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A25="","&lt;&gt;",$A25),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="36">
+        <f>IF(Kader!$A5="","",Kader!$A5)</f>
+        <v/>
+      </c>
+      <c r="B26" s="29">
+        <f>IF(Kader!$B5="","",Kader!$B5)</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M26" s="36">
+        <f>IF($A26="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="47">
+        <f>IF($A26="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A26="","&lt;&gt;",$A26),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="36">
+        <f>IF(Kader!$A6="","",Kader!$A6)</f>
+        <v/>
+      </c>
+      <c r="B27" s="29">
+        <f>IF(Kader!$B6="","",Kader!$B6)</f>
+        <v/>
+      </c>
+      <c r="C27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M27" s="36">
+        <f>IF($A27="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="47">
+        <f>IF($A27="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A27="","&lt;&gt;",$A27),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="36">
+        <f>IF(Kader!$A7="","",Kader!$A7)</f>
+        <v/>
+      </c>
+      <c r="B28" s="29">
+        <f>IF(Kader!$B7="","",Kader!$B7)</f>
+        <v/>
+      </c>
+      <c r="C28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M28" s="36">
+        <f>IF($A28="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="47">
+        <f>IF($A28="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A28="","&lt;&gt;",$A28),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="36">
+        <f>IF(Kader!$A8="","",Kader!$A8)</f>
+        <v/>
+      </c>
+      <c r="B29" s="29">
+        <f>IF(Kader!$B8="","",Kader!$B8)</f>
+        <v/>
+      </c>
+      <c r="C29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M29" s="36">
+        <f>IF($A29="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="47">
+        <f>IF($A29="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A29="","&lt;&gt;",$A29),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="36">
+        <f>IF(Kader!$A9="","",Kader!$A9)</f>
+        <v/>
+      </c>
+      <c r="B30" s="29">
+        <f>IF(Kader!$B9="","",Kader!$B9)</f>
+        <v/>
+      </c>
+      <c r="C30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M30" s="36">
+        <f>IF($A30="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="47">
+        <f>IF($A30="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A30="","&lt;&gt;",$A30),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="36">
+        <f>IF(Kader!$A10="","",Kader!$A10)</f>
+        <v/>
+      </c>
+      <c r="B31" s="29">
+        <f>IF(Kader!$B10="","",Kader!$B10)</f>
+        <v/>
+      </c>
+      <c r="C31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M31" s="36">
+        <f>IF($A31="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="47">
+        <f>IF($A31="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A31="","&lt;&gt;",$A31),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="36">
+        <f>IF(Kader!$A11="","",Kader!$A11)</f>
+        <v/>
+      </c>
+      <c r="B32" s="29">
+        <f>IF(Kader!$B11="","",Kader!$B11)</f>
+        <v/>
+      </c>
+      <c r="C32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M32" s="36">
+        <f>IF($A32="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="47">
+        <f>IF($A32="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A32="","&lt;&gt;",$A32),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="36">
+        <f>IF(Kader!$A12="","",Kader!$A12)</f>
+        <v/>
+      </c>
+      <c r="B33" s="29">
+        <f>IF(Kader!$B12="","",Kader!$B12)</f>
+        <v/>
+      </c>
+      <c r="C33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M33" s="36">
+        <f>IF($A33="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="47">
+        <f>IF($A33="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A33="","&lt;&gt;",$A33),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="36">
+        <f>IF(Kader!$A13="","",Kader!$A13)</f>
+        <v/>
+      </c>
+      <c r="B34" s="29">
+        <f>IF(Kader!$B13="","",Kader!$B13)</f>
+        <v/>
+      </c>
+      <c r="C34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M34" s="36">
+        <f>IF($A34="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="47">
+        <f>IF($A34="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A34="","&lt;&gt;",$A34),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="36">
+        <f>IF(Kader!$A14="","",Kader!$A14)</f>
+        <v/>
+      </c>
+      <c r="B35" s="29">
+        <f>IF(Kader!$B14="","",Kader!$B14)</f>
+        <v/>
+      </c>
+      <c r="C35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M35" s="36">
+        <f>IF($A35="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N35" s="47">
+        <f>IF($A35="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A35="","&lt;&gt;",$A35),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="36">
+        <f>IF(Kader!$A15="","",Kader!$A15)</f>
+        <v/>
+      </c>
+      <c r="B36" s="29">
+        <f>IF(Kader!$B15="","",Kader!$B15)</f>
+        <v/>
+      </c>
+      <c r="C36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M36" s="36">
+        <f>IF($A36="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N36" s="47">
+        <f>IF($A36="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A36="","&lt;&gt;",$A36),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="36">
+        <f>IF(Kader!$A16="","",Kader!$A16)</f>
+        <v/>
+      </c>
+      <c r="B37" s="29">
+        <f>IF(Kader!$B16="","",Kader!$B16)</f>
+        <v/>
+      </c>
+      <c r="C37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M37" s="36">
+        <f>IF($A37="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N37" s="47">
+        <f>IF($A37="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A37="","&lt;&gt;",$A37),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="36">
+        <f>IF(Kader!$A17="","",Kader!$A17)</f>
+        <v/>
+      </c>
+      <c r="B38" s="29">
+        <f>IF(Kader!$B17="","",Kader!$B17)</f>
+        <v/>
+      </c>
+      <c r="C38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M38" s="36">
+        <f>IF($A38="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N38" s="47">
+        <f>IF($A38="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A38="","&lt;&gt;",$A38),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="36">
+        <f>IF(Kader!$A18="","",Kader!$A18)</f>
+        <v/>
+      </c>
+      <c r="B39" s="29">
+        <f>IF(Kader!$B18="","",Kader!$B18)</f>
+        <v/>
+      </c>
+      <c r="C39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M39" s="36">
+        <f>IF($A39="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N39" s="47">
+        <f>IF($A39="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A39="","&lt;&gt;",$A39),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="36">
+        <f>IF(Kader!$A19="","",Kader!$A19)</f>
+        <v/>
+      </c>
+      <c r="B40" s="29">
+        <f>IF(Kader!$B19="","",Kader!$B19)</f>
+        <v/>
+      </c>
+      <c r="C40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M40" s="36">
+        <f>IF($A40="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N40" s="47">
+        <f>IF($A40="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A40="","&lt;&gt;",$A40),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="36">
+        <f>IF(Kader!$A20="","",Kader!$A20)</f>
+        <v/>
+      </c>
+      <c r="B41" s="29">
+        <f>IF(Kader!$B20="","",Kader!$B20)</f>
+        <v/>
+      </c>
+      <c r="C41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M41" s="36">
+        <f>IF($A41="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N41" s="47">
+        <f>IF($A41="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A41="","&lt;&gt;",$A41),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="36">
+        <f>IF(Kader!$A21="","",Kader!$A21)</f>
+        <v/>
+      </c>
+      <c r="B42" s="29">
+        <f>IF(Kader!$B21="","",Kader!$B21)</f>
+        <v/>
+      </c>
+      <c r="C42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M42" s="36">
+        <f>IF($A42="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N42" s="47">
+        <f>IF($A42="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A42="","&lt;&gt;",$A42),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="36">
+        <f>IF(Kader!$A22="","",Kader!$A22)</f>
+        <v/>
+      </c>
+      <c r="B43" s="29">
+        <f>IF(Kader!$B22="","",Kader!$B22)</f>
+        <v/>
+      </c>
+      <c r="C43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M43" s="36">
+        <f>IF($A43="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N43" s="47">
+        <f>IF($A43="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A43="","&lt;&gt;",$A43),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="36">
+        <f>IF(Kader!$A23="","",Kader!$A23)</f>
+        <v/>
+      </c>
+      <c r="B44" s="29">
+        <f>IF(Kader!$B23="","",Kader!$B23)</f>
+        <v/>
+      </c>
+      <c r="C44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="D44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Außen",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="E44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="F44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Kreis",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="G44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="H44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Rückraum",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="I44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="J44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Durchbruch",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="K44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="L44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Tempogegenstoß",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+      <c r="M44" s="36">
+        <f>IF($A44="","",IF((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))=0,"",(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))&amp;" / "&amp;(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf"))))</f>
+        <v/>
+      </c>
+      <c r="N44" s="47">
+        <f>IF($A44="","",IFERROR((COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor"))/(COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"Fehlwurf")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Tor")+COUNTIFS(Spielprotokoll!$A$4:$A$403,IF($B$3="","&lt;&gt;",$B$3),Spielprotokoll!$C$4:$C$403,IF($A44="","&lt;&gt;",$A44),Spielprotokoll!$F$4:$F$403,"Siebenmeter",Spielprotokoll!$E$4:$E$403,"7m Fehlwurf")),""))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B11:G11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M6:M11">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K11">
+    <cfRule type="dataBar" priority="8">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00F97316"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D44">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:F44">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H44">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25:J44">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L25:L44">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N44">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="0.2"/>
+        <cfvo type="num" val="0.45"/>
+        <cfvo type="num" val="0.75"/>
+        <color rgb="00F8B4B4"/>
+        <color rgb="00FDE68A"/>
+        <color rgb="00A7D8A0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Spiele</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002C4A5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
